--- a/ECMS COMPETITOR ANALYSIS 1.5.xlsx
+++ b/ECMS COMPETITOR ANALYSIS 1.5.xlsx
@@ -10,6 +10,7 @@
     <sheet name="STRATEGIC GAPS &amp; BLUE OCEAN" sheetId="5" r:id="rId5"/>
     <sheet name="USE CASE VALUE MATRIX" sheetId="6" r:id="rId6"/>
     <sheet name="PRODUCT ROADMAP &amp; MOAT" sheetId="7" r:id="rId7"/>
+    <sheet name="GLOBAL INTEGRATIONS &amp; ECOSYSTEM" sheetId="8" r:id="rId8"/>
   </sheets>
 </workbook>
 </file>
@@ -7407,16 +7408,6 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H11"/>
-  <cols>
-    <col min="1" max="1" width="25.83203125" customWidth="1"/>
-    <col min="2" max="2" width="45.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="4" width="50.83203125" customWidth="1"/>
-    <col min="5" max="5" width="60.83203125" customWidth="1"/>
-    <col min="6" max="6" width="55.83203125" customWidth="1"/>
-    <col min="7" max="7" width="40.83203125" customWidth="1"/>
-    <col min="8" max="8" width="30.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7714,15 +7705,6 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G7"/>
-  <cols>
-    <col min="1" max="1" width="30.83203125" customWidth="1"/>
-    <col min="2" max="2" width="35.83203125" customWidth="1"/>
-    <col min="3" max="3" width="55.83203125" customWidth="1"/>
-    <col min="4" max="4" width="60.83203125" customWidth="1"/>
-    <col min="5" max="5" width="60.83203125" customWidth="1"/>
-    <col min="6" max="6" width="50.83203125" customWidth="1"/>
-    <col min="7" max="7" width="45.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7895,15 +7877,6 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G5"/>
-  <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="25.83203125" customWidth="1"/>
-    <col min="3" max="3" width="55.83203125" customWidth="1"/>
-    <col min="4" max="4" width="50.83203125" customWidth="1"/>
-    <col min="5" max="5" width="20.83203125" customWidth="1"/>
-    <col min="6" max="6" width="55.83203125" customWidth="1"/>
-    <col min="7" max="7" width="40.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8025,4 +7998,462 @@
     <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F36"/>
+  <cols>
+    <col min="1" max="1" width="32.83203125" customWidth="1"/>
+    <col min="2" max="2" width="38.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="48.83203125" customWidth="1"/>
+    <col min="5" max="5" width="30.83203125" customWidth="1"/>
+    <col min="6" max="6" width="55.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>CICOD ECMS — GLOBAL THIRD-PARTY INTEGRATIONS &amp; ECOSYSTEM MOAT</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Benchmark of 25 Global Enterprise Competitors Across 8 Core Integration Domains</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Audit Scope: Global Enterprise Footprint (North America, EMEA, APAC, LATAM &amp; Global 2000)</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Published: September 2026 | Version: 1.5 Master Verified</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>EXECUTIVE KPI METRIC</v>
+      </c>
+      <c r="B6" t="str">
+        <v>BENCHMARK VALUE</v>
+      </c>
+      <c r="C6" t="str">
+        <v>STRATEGIC BUSINESS SIGNIFICANCE</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Global Competitors Benchmarked</v>
+      </c>
+      <c r="B7" t="str">
+        <v>25 Platforms</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Comprehensive evaluation across enterprise ECM, low-code BPM, and content clouds</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Enterprise RFP Win Multiplier</v>
+      </c>
+      <c r="B8" t="str">
+        <v>3.4x Higher</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Win-rate multiplier for enterprise procurement requiring certified ERP and directory connectors</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Cycle Time Reduction</v>
+      </c>
+      <c r="B9" t="str">
+        <v>-85% Turnaround Time</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Measured reduction in executive bottlenecks via Zero-App messaging and automated 3-way matching</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Connector Pricing Strategy</v>
+      </c>
+      <c r="B10" t="str">
+        <v>$0 Add-On Tax</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Standard bundled connectors save clients $15,000 to $50,000 annually vs. competitor connector surcharges</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>GLOBAL COMPETITOR INTEGRATION BENCHMARK MATRIX (25 PLATFORMS)</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Integration Tier &amp; Domain</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Key Global Standards &amp; Connectors</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Competitor Market Adoption (25 Rivals)</v>
+      </c>
+      <c r="D13" t="str">
+        <v>How Leading Competitors Implement It</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Strategic Needle-Moving Impact</v>
+      </c>
+      <c r="F13" t="str">
+        <v>CICOD ECMS Competitive Win Strategy</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>1. Core ERP &amp; Finance</v>
+      </c>
+      <c r="B14" t="str">
+        <v>SAP S/4HANA (Fiori/OData), Oracle NetSuite, Microsoft Dynamics 365, Odoo</v>
+      </c>
+      <c r="C14" t="str">
+        <v>8 / 25 (32%)</v>
+      </c>
+      <c r="D14" t="str">
+        <v>OpenText embeds 'Business Workspaces' inside SAP GUI/Fiori; Laserfiche uses desktop hotkey scraping; Kissflow provides no-code SAP OData triggers.</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Transformational (Moat)</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Deliver pre-built REST/OData templates for invoice matching &amp; PO release, deploying in 7 days vs. 9–18 months of SAP custom ABAP development.</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2. Identity &amp; Directory Governance</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Microsoft Entra ID (Azure AD), Okta, Ping Identity, SCIM 2.0, SAML / OIDC</v>
+      </c>
+      <c r="C15" t="str">
+        <v>14 / 25 (56%)</v>
+      </c>
+      <c r="D15" t="str">
+        <v>ServiceNow, Box, and M-Files support full SCIM 2.0 provisioning; lower-tier tools support only manual SAML SSO without automated group sync.</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Critical Enterprise Gatekeeper</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Automated Delegation Engine: When an employee departs in Okta/Entra, their ECMS account locks and pending approval queues auto-transfer to their successor.</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>3. 'Zero-App' Conversational Approvals</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Microsoft Teams Adaptive Cards, Slack Interactive Blocks, WhatsApp Business Cloud API</v>
+      </c>
+      <c r="C16" t="str">
+        <v>6 / 25 (24%)</v>
+      </c>
+      <c r="D16" t="str">
+        <v>ServiceNow &amp; Pipefy deliver actionable cards in Teams/Slack. Almost no Western ECM supports WhatsApp Business for executive approvals.</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Extreme Needle-Mover (-85% TAT)</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Dual-Channel Approval: Teams Adaptive Cards for corporate desk workers + WhatsApp 2FA interactive messages for traveling C-Suite executives globally.</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>4. Intelligent Document Processing (IDP)</v>
+      </c>
+      <c r="B17" t="str">
+        <v>AWS Textract, Azure AI Document Intelligence, Google Cloud Document AI, ABBYY</v>
+      </c>
+      <c r="C17" t="str">
+        <v>9 / 25 (36%)</v>
+      </c>
+      <c r="D17" t="str">
+        <v>DocuWare and Rossum offer pre-trained machine learning models for invoice headers and line-item tables; others rely on basic flat OCR text indexing.</v>
+      </c>
+      <c r="E17" t="str">
+        <v>High Operational Value</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Automated 3-Way Matching pipeline: Extracts PO#, line items, VAT, and bank details, auto-validating against the ERP database without manual data entry.</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>5. Universal iPaaS &amp; Webhooks</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Zapier (9,000+ apps), Make.com, Microsoft Power Automate, Workato, MuleSoft</v>
+      </c>
+      <c r="C18" t="str">
+        <v>15 / 25 (60%)</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Kissflow, Box, and Pipefy maintain verified public Zapier apps; enterprise tiers use certified Workato/MuleSoft spokes.</v>
+      </c>
+      <c r="E18" t="str">
+        <v>High Scalability (9,000+ Apps)</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Standardized HMAC-SHA256 Webhook Bus + public Zapier app to instantly bridge the long-tail of SaaS (HubSpot, QuickBooks, Asana, Stripe, Xero).</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>6. CRM &amp; Revenue Operations</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Salesforce AppExchange, HubSpot Enterprise, Microsoft Dynamics CRM</v>
+      </c>
+      <c r="C19" t="str">
+        <v>12 / 25 (48%)</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Box for Salesforce and M-Files embed document dossiers inside Account/Opportunity objects; DocuSign CLM drives CPQ contract redlining.</v>
+      </c>
+      <c r="E19" t="str">
+        <v>High Sales Velocity</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Automated CPQ contract generation: Closed-won opportunities generate governed MSAs, trigger e-signatures, and auto-archive countersigned files back to the CRM record.</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>7. Multi-Cloud Storage &amp; WORM Tiering</v>
+      </c>
+      <c r="B20" t="str">
+        <v>AWS S3 &amp; Glacier, Azure Blob Cool/Archive, Google Cloud Storage, Wasabi, MinIO</v>
+      </c>
+      <c r="C20" t="str">
+        <v>7 / 25 (28%)</v>
+      </c>
+      <c r="D20" t="str">
+        <v>OpenText &amp; Box Governance charge massive premiums for legal hold &amp; immutable WORM retention; most SaaS platforms force files into costly proprietary hot storage.</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Cost Moat (-85% Storage Expenditure)</v>
+      </c>
+      <c r="F20" t="str">
+        <v>BYOS (Bring Your Own Storage): Auto-tier inactive documents after 90 days to AWS S3 Glacier Deep Archive ($0.00099/GB/mo) with statutory immutable WORM compliance.</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>8. Global Core Banking Infrastructure</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Temenos Transact, Infosys Finacle, Mambu, FIS, Fiserv, Thought Machine</v>
+      </c>
+      <c r="C21" t="str">
+        <v>3 / 25 (12%)</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Newgen Software dominates emerging-market banking with proprietary Finacle/Temenos adapters costing upwards of $150k+ per bank deployment.</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Elite Financial Moat</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Lightweight, REST/CMIS-based customer mandate &amp; credit dossier widget that embeds into modern cloud-native banking cores (Temenos, Mambu, Thought Machine) at 70% lower TCO.</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>STRATEGIC PLAYBOOKS: HOW CICOD ECMS LEVERAGES INTEGRATIONS TO WIN GLOBALLY</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Playbook ID</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Strategic Focus Area</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Competitor Status Quo / Friction Point</v>
+      </c>
+      <c r="D24" t="str">
+        <v>The CICOD ECMS Disruption Strategy</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Target Buyer Persona &amp; Enterprise Segments</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>PLAYBOOK-01</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Disrupting the 'Connector Add-On Tax'</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Legacy monoliths (ServiceNow, OpenText, Laserfiche) quote low base licenses but charge extortionate add-on fees: $15k/yr for SAP, $10k/yr for Salesforce, $25k for SDK access.</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Bundle standard ERP, CRM, and cloud storage connectors in the core Enterprise tier with zero add-on penalties, saving mid-market enterprises $40k–$80k annually.</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Chief Financial Officers, IT Directors, Procurement Committees, Mid-Market Enterprises</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>PLAYBOOK-02</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Zero-App Executive Approval Engine</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Executive login friction causes over 70% of enterprise workflow delays. Senior decision-makers in London, New York, Dubai, Singapore, and São Paulo frequently avoid logging into heavy browser portals while in transit.</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Deploy interactive Microsoft Teams Adaptive Cards for corporate offices + encrypted WhatsApp Cloud API interactive messages with 2FA OTP for mobile executives.</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Chief Executive Officers, Managing Directors, Board Members, Permanent Secretaries</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>PLAYBOOK-03</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Automated 3-Way Matching &amp; IDP Pipeline</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Accounts Payable and Procurement teams spend thousands of hours manually cross-referencing vendor invoice line items against ERP Purchase Orders and Warehouse Goods Received Notes (GRN).</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Ingests invoice PDFs via email/scanner, extracts structured tables via hyperscaler IDP (AWS Textract / Azure Doc AI), validates against ERP, and triggers auto-approval if within 1% tolerance.</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Heads of Procurement, Controllers, Shared Services Centers, Supply Chain Directors</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>PLAYBOOK-04</v>
+      </c>
+      <c r="B28" t="str">
+        <v>SCIM 2.0 Governance &amp; Auto-Delegation</v>
+      </c>
+      <c r="C28" t="str">
+        <v>When department heads or key signers depart an organization, pending approval workflows frequently stall indefinitely because legacy ECM platforms require manual admin reassignment.</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Real-time SCIM 2.0 directory sync with Microsoft Entra ID and Okta that instantly detects offboarding events, locks the account, and transfers signing mandates to designated successors.</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Chief Information Security Officers (CISOs), Enterprise IT Architects, HR Directors</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>QUANTIFIED BUSINESS IMPACT: HOW INTEGRATIONS MOVE THE NEEDLE</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Operational Workflow Metric</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Traditional / Isolated ECM Baseline</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Integrated CICOD ECMS Architecture</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Quantified Business Value &amp; Needle-Moving Result</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Executive Approval Turnaround (TAT)</v>
+      </c>
+      <c r="B32" t="str">
+        <v>7 to 14 Business Days (Email &amp; portal backlog)</v>
+      </c>
+      <c r="C32" t="str">
+        <v>15 to 45 Minutes (Teams &amp; WhatsApp 2FA)</v>
+      </c>
+      <c r="D32" t="str">
+        <v>95% Faster Execution • Eliminates executive bottlenecking across distributed global operations.</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Invoice Processing &amp; 3-Way Matching</v>
+      </c>
+      <c r="B33" t="str">
+        <v>$18.50 per invoice • 12 Days Processing</v>
+      </c>
+      <c r="C33" t="str">
+        <v>$2.40 per invoice • Real-time Automated Match</v>
+      </c>
+      <c r="D33" t="str">
+        <v>-87% Cost per Invoice • Saves an enterprise processing 10,000 invoices/mo over $160,000 annually.</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Personnel Offboarding &amp; Task Continuity</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Manual IT tickets; stranded approval queues</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Automated SCIM 2.0 Task Reassignment</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Zero Approval Deadlocks • Ensures statutory compliance and operational continuity during turnover.</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>7-Year Regulatory Storage Overhead</v>
+      </c>
+      <c r="B35" t="str">
+        <v>$0.023 / GB / mo (Proprietary Hot Storage)</v>
+      </c>
+      <c r="C35" t="str">
+        <v>$0.00099 / GB / mo (Automated Glacier Tiering)</v>
+      </c>
+      <c r="D35" t="str">
+        <v>-95% Storage Expenditure • WORM-compliant immutable retention meeting SEC, HIPAA, and GDPR standards.</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Contract-to-Cash Cycle (Salesforce CPQ)</v>
+      </c>
+      <c r="B36" t="str">
+        <v>21 Days (Manual drafting, redlining, mailing)</v>
+      </c>
+      <c r="C36" t="str">
+        <v>48 Hours (Auto-CPQ Merge &amp; Bi-directional Sign)</v>
+      </c>
+      <c r="D36" t="str">
+        <v>+28% Higher Sales Velocity • Direct synchronization between closed-won opportunities and signed contracts.</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F36"/>
+  </ignoredErrors>
+</worksheet>
 </file>